--- a/reports/readability_dev.xlsx
+++ b/reports/readability_dev.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Readability rating of obfuscated variants (Section 3.2.3)</t>
+          <t>Readability and meaning rating of obfuscated variants (Section 3.2.3)</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Each sheet A, B, C is for one rater. Rate only your own sheet. The 20 rows are the obfuscated variants (obf_low, obf_high) of the development sample; original_body is the untouched email, variant_body the obfuscated one. Read variant_body as a recipient would, without the original.</t>
+          <t>Each sheet A, B, C is for one rater. Rate only your own sheet. The 20 rows are the obfuscated variants (obf_low, obf_high) of the development sample; original_body is the untouched email, variant_body the obfuscated one. This workbook shows the text exactly as stored (the first-round file was displayed by Excel in the wrong code page, so these rows are rated again here).</t>
         </is>
       </c>
     </row>
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Choose one value in the readability column (drop-down):</t>
+          <t>Step 1, readability: read variant_body as a recipient would, without the original, and choose one value in the readability column (drop-down):</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,38 @@
       <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Step 2, meaning: compare variant_body with original_body and choose one value in the meaning column (drop-down), using the same scale as in the first round:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>preserved = the variant conveys the same information and the same request as the original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>partly = some information is changed, lost or added, but the main request is still the same.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>not = the main request or a key fact (who, what, when, how much, where to act) is changed or missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Do not edit any other column. Do not correct the text. Save the workbook under the same name.</t>
         </is>
@@ -505,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -514,6 +545,7 @@
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,6 +577,11 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>readability</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
         </is>
       </c>
     </row>
@@ -587,6 +624,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -629,6 +667,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -667,6 +706,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -709,6 +749,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -747,6 +788,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -785,6 +827,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -821,6 +864,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -859,6 +903,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -901,6 +946,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -933,6 +979,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -969,6 +1016,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1001,6 +1049,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1043,6 +1092,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1085,6 +1135,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1125,6 +1176,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1163,6 +1215,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1199,6 +1252,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1237,6 +1291,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1275,6 +1330,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1317,11 +1373,15 @@
         </is>
       </c>
       <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1334,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1343,6 +1403,7 @@
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1374,6 +1435,11 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>readability</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
         </is>
       </c>
     </row>
@@ -1416,6 +1482,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1458,6 +1525,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1496,6 +1564,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1538,6 +1607,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1576,6 +1646,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1614,6 +1685,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1650,6 +1722,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1688,6 +1761,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1730,6 +1804,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1762,6 +1837,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1798,6 +1874,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1830,6 +1907,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1872,6 +1950,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1914,6 +1993,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1954,6 +2034,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1992,6 +2073,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2028,6 +2110,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2066,6 +2149,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2104,6 +2188,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2146,11 +2231,15 @@
         </is>
       </c>
       <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2163,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2261,7 @@
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="70" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2203,6 +2293,11 @@
       <c r="F1" s="3" t="inlineStr">
         <is>
           <t>readability</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
         </is>
       </c>
     </row>
@@ -2245,6 +2340,7 @@
         </is>
       </c>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2287,6 +2383,7 @@
         </is>
       </c>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2325,6 +2422,7 @@
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2367,6 +2465,7 @@
         </is>
       </c>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2405,6 +2504,7 @@
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2443,6 +2543,7 @@
         </is>
       </c>
       <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -2479,6 +2580,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2517,6 +2619,7 @@
         </is>
       </c>
       <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2559,6 +2662,7 @@
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2591,6 +2695,7 @@
         </is>
       </c>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2627,6 +2732,7 @@
         </is>
       </c>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2659,6 +2765,7 @@
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -2701,6 +2808,7 @@
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2743,6 +2851,7 @@
         </is>
       </c>
       <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2783,6 +2892,7 @@
         </is>
       </c>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2821,6 +2931,7 @@
         </is>
       </c>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2857,6 +2968,7 @@
         </is>
       </c>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2895,6 +3007,7 @@
         </is>
       </c>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2933,6 +3046,7 @@
         </is>
       </c>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2975,11 +3089,15 @@
         </is>
       </c>
       <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/readability_dev.xlsx
+++ b/reports/readability_dev.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="para_changed_A" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="para_changed_B" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="para_changed_C" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -519,7 +522,17 @@
       <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Sheets para_changed_A / _B / _C: 8 paraphrased variants whose accepted text changed when the similarity threshold was fixed (the text you rated in the first round was a different rewrite of the same email). Rate the meaning of the NEW variant_body against original_body with the same scale. These rows have no readability column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Do not edit any other column. Do not correct the text. Save the workbook under the same name.</t>
         </is>
@@ -1377,10 +1390,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
+    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
       <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2235,10 +2248,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
+    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
       <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3093,10 +3106,1084 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter 2, 1 or 0 (see the Instructions sheet)" type="list">
+    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
       <formula1>"2,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter preserved, partly or not (see the Instructions sheet)" type="list">
+    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>original_body</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>variant_body</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_low</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_low</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>eph:11434#para_high</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
+Please use the secure portal provided to confirm your credentials: the link.
+Let me know once you've done this, so I can proceed with the necessary adjustments.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
+Kindly utilize the protected website indicated to verify your identity: the link.
+Please inform me upon completion, allowing me to make the required modifications.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>eph:14108#para_high</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
+the link
+Let's make sure everyone is on the same page.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
+the link
+Ensure that all parties are aligned and informed.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>eph:15264#para_high</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
+Link to download: the link
+Let me know if you need any further information.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
+Link to download: the link
+Please inform me if additional details are required.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_high</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>eph:4123#para_high</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
+To avoid disruption, we urge you to download our comprehensive repair tool from the following link: the link. This tool has been crafted meticulously by our engineers to address the specific issues at hand.
+Please prioritize this task to ensure your devices are running smoothly and securely.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
+In order to prevent any interruption, we strongly recommend that you acquire our full-fledged repair software from the subsequent link: the link. Our engineers have painstakingly developed this instrument to effectively tackle the particular challenges presented.
+Ensure the prioritization of this task to guarantee your gadgets operate efficiently and with enhanced security.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>original_body</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>variant_body</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_low</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_low</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>eph:11434#para_high</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
+Please use the secure portal provided to confirm your credentials: the link.
+Let me know once you've done this, so I can proceed with the necessary adjustments.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
+Kindly utilize the protected website indicated to verify your identity: the link.
+Please inform me upon completion, allowing me to make the required modifications.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>eph:14108#para_high</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
+the link
+Let's make sure everyone is on the same page.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
+the link
+Ensure that all parties are aligned and informed.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>eph:15264#para_high</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
+Link to download: the link
+Let me know if you need any further information.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
+Link to download: the link
+Please inform me if additional details are required.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_high</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>eph:4123#para_high</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
+To avoid disruption, we urge you to download our comprehensive repair tool from the following link: the link. This tool has been crafted meticulously by our engineers to address the specific issues at hand.
+Please prioritize this task to ensure your devices are running smoothly and securely.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
+In order to prevent any interruption, we strongly recommend that you acquire our full-fledged repair software from the subsequent link: the link. Our engineers have painstakingly developed this instrument to effectively tackle the particular challenges presented.
+Ensure the prioritization of this task to guarantee your gadgets operate efficiently and with enhanced security.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
+      <formula1>"preserved,partly,not"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>variant_id</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>original_body</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>variant_body</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_low</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_low</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>para_low</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>eph:11434#para_high</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
+Please use the secure portal provided to confirm your credentials: the link.
+Let me know once you've done this, so I can proceed with the necessary adjustments.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Hello David,
+I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
+Kindly utilize the protected website indicated to verify your identity: the link.
+Please inform me upon completion, allowing me to make the required modifications.
+Best regards,
+John Smith
+Senior Operations Analyst</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>eph:12308#para_high</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
+the link
+Thanks a ton!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hey James,
+Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
+the link
+Immeasurable gratitude expressed!
+Best,
+Cassie Hamilton
+(Senior Operations Manager)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>eph:14108#para_high</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
+the link
+Let's make sure everyone is on the same page.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Hi Callum,
+Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
+the link
+Ensure that all parties are aligned and informed.
+Cheers,
+Alex Martins</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>eph:15264#para_high</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
+Link to download: the link
+Let me know if you need any further information.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Hello Joel,
+I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
+Link to download: the link
+Please inform me if additional details are required.
+Take care,
+Michael Green
+Sustainability Coordinator</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>eph:16367#para_high</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Hey Michael,
+I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
+Thank you!
+Best,
+Jake
+Operations Team</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>eph:4123#para_high</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>para_high</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
+To avoid disruption, we urge you to download our comprehensive repair tool from the following link: the link. This tool has been crafted meticulously by our engineers to address the specific issues at hand.
+Please prioritize this task to ensure your devices are running smoothly and securely.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Dear Gerald,
+We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
+In order to prevent any interruption, we strongly recommend that you acquire our full-fledged repair software from the subsequent link: the link. Our engineers have painstakingly developed this instrument to effectively tackle the particular challenges presented.
+Ensure the prioritization of this task to guarantee your gadgets operate efficiently and with enhanced security.
+Regards,
+Tech Support Team
+--- This message is intended for immediate action ---</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
       <formula1>"preserved,partly,not"</formula1>
     </dataValidation>
   </dataValidations>

--- a/reports/readability_dev.xlsx
+++ b/reports/readability_dev.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +34,6 @@
     <font>
       <b val="1"/>
     </font>
-    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -44,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,21 +51,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,9 +433,6 @@
   </sheetPr>
   <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -446,93 +441,83 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Each sheet A, B, C is for one rater. Rate only your own sheet. The 20 rows are the obfuscated variants (obf_low, obf_high) of the development sample; original_body is the untouched email, variant_body the obfuscated one. This workbook shows the text exactly as stored (the first-round file was displayed by Excel in the wrong code page, so these rows are rated again here).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Step 1, readability: read variant_body as a recipient would, without the original, and choose one value in the readability column (drop-down):</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2 = reads normally: nothing stands out, every word is read without effort.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>1 = noticeably odd but every word readable: spelling, spacing or characters look wrong in places, yet every word can still be recognised.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>0 = at least one word unrecognisable: at least one word cannot be read at all.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Step 2, meaning: compare variant_body with original_body and choose one value in the meaning column (drop-down), using the same scale as in the first round:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>preserved = the variant conveys the same information and the same request as the original.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>partly = some information is changed, lost or added, but the main request is still the same.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>not = the main request or a key fact (who, what, when, how much, where to act) is changed or missing.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Sheets para_changed_A / _B / _C: 8 paraphrased variants whose accepted text changed when the similarity threshold was fixed (the text you rated in the first round was a different rewrite of the same email). Rate the meaning of the NEW variant_body against original_body with the same scale. These rows have no readability column.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Do not edit any other column. Do not correct the text. Save the workbook under the same name.</t>
         </is>
@@ -551,68 +536,59 @@
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>readability</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12072#obf_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document with you, which needs your immediate review.
@@ -624,7 +600,7 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document wit​h you, which nee​ds yo.ur immediate review.
@@ -636,24 +612,30 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:12240#obf_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -666,7 +648,7 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -679,24 +661,30 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:12308#obf_low</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -707,7 +695,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope yo.ur day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smooth​ly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -718,24 +706,30 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12798#obf_low</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 This is a reminder that the invoice for order #: 5498 from July 2023 remains unsettled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -748,7 +742,7 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 Thіs is a reminde.r that the invoice for order #: 5498 from July 2023 remains unse​ttled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -761,24 +755,30 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:15539#obf_low</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this message finds you well. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -789,7 +789,7 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this messаge finds you w3ll. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -800,24 +800,30 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:16547#obf_low</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hope you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you might have the most updated access credentials. Could you send them over to ensure everything is synced on our end?
@@ -828,7 +834,7 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hоpe you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you mіght have the most updated ac​cess credеntials. Could you send them over to ensure everything is synced on our end?
@@ -839,24 +845,30 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:1743#obf_low</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve been well since our last meeting about the new handbag redesign. I wanted to quickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -866,7 +878,7 @@
 the link</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve beеn well since our last meeting about the new handbag redesign. I wanted to qu​ickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -876,24 +888,30 @@
 the link</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#obf_low</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -904,7 +922,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the n3twork capabilities of your device that needs immediate attention. Our records indicate that your 3quipment might be experiencing malfunctions, which co.uld interfere with your day-to-day operations.
@@ -915,24 +933,30 @@
 --- This me​ssage is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>eph:4299#obf_low</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -945,7 +969,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent reque.st regarding a critical payment to one of our major suppliers. Due to the ti​me-sensitive nature, please arrange a trans.fer of €50,000 to the account provided in the link below by EOD.
@@ -958,24 +982,30 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>eph:5551#obf_low</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discuss with you. Could you send me the latest data report? It would be super helpful for our next meeting.
@@ -983,7 +1013,7 @@
 Florian</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discu.ss with you. Could you sen.d me the latest data report? It would be super helpful for our next meeting.
@@ -991,24 +1021,30 @@
 Floria​n</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>eph:11422#obf_high</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Please process the transfer of funds for our latest venture. It's crucial that these resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -1018,7 +1054,7 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Plеase process the transf​er of funds for our lаtest venture. It's cru-cial that th​ese resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -1028,24 +1064,30 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>eph:11795#obf_high</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your time with us at Atlantic Coast Media Group! As we implement some necessary system updates, we kindly ask you to verify your email account details to ensure continued access. Please follow this secure link: the link.
@@ -1053,7 +1095,7 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your ti​me with us at Atlantic Coast Media Grouр! As we implement som​e necessary syst​em updates, we kindly ask you to verify y0ur email account details to еnsure continued access. Please fo1low this secure 1ink: the link.
@@ -1061,24 +1103,30 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>eph:11938#obf_high</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Dear Ms. Harris,
 This is a friendly reminder that Invoice #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for your reference.
@@ -1091,7 +1139,7 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>De​ar Ms. Harris,
 This is a friendly reminder that Invoic​e #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for you.r ref​erence.
@@ -1104,24 +1152,30 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>eph:12001#obf_high</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourism project management experience. This update includes:
@@ -1134,7 +1188,7 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourіsm proj3ct managem-ent experience. This update includes:
@@ -1147,24 +1201,30 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>eph:12580#obf_high</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hope this message finds you well. As we are in the critical stages of finalizing our current shipping routes optimization project, I need you to confirm your login credentials to grant you continued access to all necessary documents and platforms.
@@ -1176,7 +1236,7 @@
 Senior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hopе this message finds you well. As we are in the critical stages of finalizing our current 5hipping routеs optimization project, I nee.d you to confirm your login crede​ntials to grant you continued access to all necessary docu.ments and platfоrms.
@@ -1188,24 +1248,30 @@
 S3nior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>eph:12678#obf_high</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Member,
 Our records indicate that your account is due for a mandatory security update. To prevent any disruption in service, we require you to reset your password immediately using the secure portal linked below:
@@ -1216,7 +1282,7 @@
 IT Department</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Mеmber,
 Our records indicate that your account is due for a m4ndatory security upd4te. To рrevent any disruption in service, we requirе you to r3set your password immediately using the secure portal linkеd bel0w:
@@ -1227,24 +1293,30 @@
 IT Department</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>eph:12998#obf_high</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing well. I've sent over a crucial file pertaining to the CRM project that needs your input. It's essential to review this document as soon as possible to keep our timelines intact.
@@ -1254,7 +1326,7 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing wеll. I've se​nt ov​er a crucial file рertaining to the CRM pro​ject that needs your input. It's essential to review this documеnt as soon as possibl-e to keep our timelines intact.
@@ -1264,24 +1336,30 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>eph:13135#obf_high</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Hello James,
 We hope you're doing well. As a trusted provider, we are writing to inform you about a critical update for the marketing analysis tool your department frequently uses.
@@ -1292,7 +1370,7 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hell.o James,
 We hope you're doing well. As a trusted pr-ovider, we are writing to inform you abоut a critical update for the marketing anal​ysis tоol your department frequently usеs.
@@ -1303,24 +1381,30 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>eph:13635#obf_high</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining robust security standards, it's critical that you review the attached document detailing the latest updates to our security protocols.
@@ -1331,7 +1415,7 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining ro-bust security standаrds, it's critical th4t you review the attached doc-ument detailing the late​st upda.tes to our security protocols.
@@ -1342,24 +1426,30 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>eph:4299#obf_high</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -1372,7 +1462,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reach.ing out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sens​itive nature, please arrange a tran5fer of €50,000 to the account provided in the link below by EOD.
@@ -1385,18 +1475,16 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
-      <formula1>"2,1,0"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1409,68 +1497,59 @@
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>readability</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12072#obf_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document with you, which needs your immediate review.
@@ -1482,7 +1561,7 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document wit​h you, which nee​ds yo.ur immediate review.
@@ -1494,24 +1573,30 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:12240#obf_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -1524,7 +1609,7 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -1537,24 +1622,30 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:12308#obf_low</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -1565,7 +1656,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope yo.ur day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smooth​ly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -1576,24 +1667,30 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12798#obf_low</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 This is a reminder that the invoice for order #: 5498 from July 2023 remains unsettled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -1606,7 +1703,7 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 Thіs is a reminde.r that the invoice for order #: 5498 from July 2023 remains unse​ttled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -1619,24 +1716,30 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:15539#obf_low</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this message finds you well. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -1647,7 +1750,7 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this messаge finds you w3ll. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -1658,24 +1761,30 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:16547#obf_low</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hope you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you might have the most updated access credentials. Could you send them over to ensure everything is synced on our end?
@@ -1686,7 +1795,7 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hоpe you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you mіght have the most updated ac​cess credеntials. Could you send them over to ensure everything is synced on our end?
@@ -1697,24 +1806,30 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:1743#obf_low</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve been well since our last meeting about the new handbag redesign. I wanted to quickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -1724,7 +1839,7 @@
 the link</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve beеn well since our last meeting about the new handbag redesign. I wanted to qu​ickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -1734,24 +1849,30 @@
 the link</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#obf_low</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -1762,7 +1883,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the n3twork capabilities of your device that needs immediate attention. Our records indicate that your 3quipment might be experiencing malfunctions, which co.uld interfere with your day-to-day operations.
@@ -1773,24 +1894,30 @@
 --- This me​ssage is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>eph:4299#obf_low</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -1803,7 +1930,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent reque.st regarding a critical payment to one of our major suppliers. Due to the ti​me-sensitive nature, please arrange a trans.fer of €50,000 to the account provided in the link below by EOD.
@@ -1816,24 +1943,30 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>eph:5551#obf_low</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discuss with you. Could you send me the latest data report? It would be super helpful for our next meeting.
@@ -1841,7 +1974,7 @@
 Florian</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discu.ss with you. Could you sen.d me the latest data report? It would be super helpful for our next meeting.
@@ -1849,24 +1982,30 @@
 Floria​n</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>eph:11422#obf_high</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Please process the transfer of funds for our latest venture. It's crucial that these resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -1876,7 +2015,7 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Plеase process the transf​er of funds for our lаtest venture. It's cru-cial that th​ese resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -1886,24 +2025,30 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>eph:11795#obf_high</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your time with us at Atlantic Coast Media Group! As we implement some necessary system updates, we kindly ask you to verify your email account details to ensure continued access. Please follow this secure link: the link.
@@ -1911,7 +2056,7 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your ti​me with us at Atlantic Coast Media Grouр! As we implement som​e necessary syst​em updates, we kindly ask you to verify y0ur email account details to еnsure continued access. Please fo1low this secure 1ink: the link.
@@ -1919,24 +2064,30 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>eph:11938#obf_high</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Dear Ms. Harris,
 This is a friendly reminder that Invoice #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for your reference.
@@ -1949,7 +2100,7 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>De​ar Ms. Harris,
 This is a friendly reminder that Invoic​e #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for you.r ref​erence.
@@ -1962,24 +2113,30 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>eph:12001#obf_high</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourism project management experience. This update includes:
@@ -1992,7 +2149,7 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourіsm proj3ct managem-ent experience. This update includes:
@@ -2005,24 +2162,30 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>eph:12580#obf_high</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hope this message finds you well. As we are in the critical stages of finalizing our current shipping routes optimization project, I need you to confirm your login credentials to grant you continued access to all necessary documents and platforms.
@@ -2034,7 +2197,7 @@
 Senior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hopе this message finds you well. As we are in the critical stages of finalizing our current 5hipping routеs optimization project, I nee.d you to confirm your login crede​ntials to grant you continued access to all necessary docu.ments and platfоrms.
@@ -2046,24 +2209,30 @@
 S3nior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>eph:12678#obf_high</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Member,
 Our records indicate that your account is due for a mandatory security update. To prevent any disruption in service, we require you to reset your password immediately using the secure portal linked below:
@@ -2074,7 +2243,7 @@
 IT Department</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Mеmber,
 Our records indicate that your account is due for a m4ndatory security upd4te. To рrevent any disruption in service, we requirе you to r3set your password immediately using the secure portal linkеd bel0w:
@@ -2085,24 +2254,30 @@
 IT Department</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>eph:12998#obf_high</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing well. I've sent over a crucial file pertaining to the CRM project that needs your input. It's essential to review this document as soon as possible to keep our timelines intact.
@@ -2112,7 +2287,7 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing wеll. I've se​nt ov​er a crucial file рertaining to the CRM pro​ject that needs your input. It's essential to review this documеnt as soon as possibl-e to keep our timelines intact.
@@ -2122,24 +2297,30 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>eph:13135#obf_high</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Hello James,
 We hope you're doing well. As a trusted provider, we are writing to inform you about a critical update for the marketing analysis tool your department frequently uses.
@@ -2150,7 +2331,7 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hell.o James,
 We hope you're doing well. As a trusted pr-ovider, we are writing to inform you abоut a critical update for the marketing anal​ysis tоol your department frequently usеs.
@@ -2161,24 +2342,30 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>eph:13635#obf_high</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining robust security standards, it's critical that you review the attached document detailing the latest updates to our security protocols.
@@ -2189,7 +2376,7 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining ro-bust security standаrds, it's critical th4t you review the attached doc-ument detailing the late​st upda.tes to our security protocols.
@@ -2200,24 +2387,30 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>eph:4299#obf_high</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -2230,7 +2423,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reach.ing out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sens​itive nature, please arrange a tran5fer of €50,000 to the account provided in the link below by EOD.
@@ -2243,18 +2436,16 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
-      <formula1>"2,1,0"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2267,68 +2458,59 @@
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>readability</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12072#obf_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document with you, which needs your immediate review.
@@ -2340,7 +2522,7 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hi Gabriella,
 I was going over our quarterly budget for operational expenses and noticed some line items that require your insights before our finance team can finalize the reports. I have shared the relevant document wit​h you, which nee​ds yo.ur immediate review.
@@ -2352,24 +2534,30 @@
 Finance Department</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:12240#obf_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -2382,7 +2570,7 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hi Carlos,
 I hope this finds you well. We're reviewing the latest developments on the pilot training enhancements project, and I need your input on a proposed change in the software architecture. This is crucial for aligning our developments with the new objectives set for next quarter.
@@ -2395,24 +2583,30 @@
 Southwest AeroTech</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:12308#obf_low</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -2423,7 +2617,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hey James,
 Hope yo.ur day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smooth​ly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -2434,24 +2628,30 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12798#obf_low</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 This is a reminder that the invoice for order #: 5498 from July 2023 remains unsettled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -2464,7 +2664,7 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Dear Accounts Department,
 Thіs is a reminde.r that the invoice for order #: 5498 from July 2023 remains unse​ttled. We urge you to process the payment at your earliest convenience to avoid late fee charges.
@@ -2477,24 +2677,30 @@
 Artistic Furnish Suppliers Attachment: Invoice_5498.pdf</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:15539#obf_low</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this message finds you well. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -2505,7 +2711,7 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dear Diego,
 I hope this messаge finds you w3ll. I need your immediate assistance with a critical issue involving our network security. It appears there might be a vulnerability that needs addressing, and I need your expertise on this.
@@ -2516,24 +2722,30 @@
 Senior Manager, Liguria Eccellenze Nautiche</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:16547#obf_low</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hope you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you might have the most updated access credentials. Could you send them over to ensure everything is synced on our end?
@@ -2544,7 +2756,7 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hi Ahmed,
 I hоpe you're doing well. Could you please do me a quick favor? We need to verify some details for the cloud management portal, and I realized you mіght have the most updated ac​cess credеntials. Could you send them over to ensure everything is synced on our end?
@@ -2555,24 +2767,30 @@
 SkyTech Associated Complaints</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:1743#obf_low</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve been well since our last meeting about the new handbag redesign. I wanted to quickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -2582,7 +2800,7 @@
 the link</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hi Walter,
 Hope you’ve beеn well since our last meeting about the new handbag redesign. I wanted to qu​ickly touch base with you on something I might have forgotten to mention. Could you check this link regarding tonight’s revisions? It’s important we stay on the same page to avoid any mix-ups before the deadline.
@@ -2592,24 +2810,30 @@
 the link</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#obf_low</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -2620,7 +2844,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the n3twork capabilities of your device that needs immediate attention. Our records indicate that your 3quipment might be experiencing malfunctions, which co.uld interfere with your day-to-day operations.
@@ -2631,24 +2855,30 @@
 --- This me​ssage is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>eph:4299#obf_low</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -2661,7 +2891,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent reque.st regarding a critical payment to one of our major suppliers. Due to the ti​me-sensitive nature, please arrange a trans.fer of €50,000 to the account provided in the link below by EOD.
@@ -2674,24 +2904,30 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>eph:5551#obf_low</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>obf_low</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discuss with you. Could you send me the latest data report? It would be super helpful for our next meeting.
@@ -2699,7 +2935,7 @@
 Florian</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Hi Inga,
 I hope you're doing well! I was reviewing our recent analytics project, and there are a few points I'd like to discu.ss with you. Could you sen.d me the latest data report? It would be super helpful for our next meeting.
@@ -2707,24 +2943,30 @@
 Floria​n</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>eph:11422#obf_high</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Please process the transfer of funds for our latest venture. It's crucial that these resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -2734,7 +2976,7 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Hi Evelyn,
 Plеase process the transf​er of funds for our lаtest venture. It's cru-cial that th​ese resources are available immediately for strategic operations. Use the attached account details to ensure seamless completion.
@@ -2744,24 +2986,30 @@
 CEO, Maple Leaf Organic Farms</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>eph:11795#obf_high</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your time with us at Atlantic Coast Media Group! As we implement some necessary system updates, we kindly ask you to verify your email account details to ensure continued access. Please follow this secure link: the link.
@@ -2769,7 +3017,7 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hi James,
 We hope you're enjoying your ti​me with us at Atlantic Coast Media Grouр! As we implement som​e necessary syst​em updates, we kindly ask you to verify y0ur email account details to еnsure continued access. Please fo1low this secure 1ink: the link.
@@ -2777,24 +3025,30 @@
 Your IT Support Team</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>eph:11938#obf_high</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Dear Ms. Harris,
 This is a friendly reminder that Invoice #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for your reference.
@@ -2807,7 +3061,7 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>De​ar Ms. Harris,
 This is a friendly reminder that Invoic​e #34829 from our company remains unpaid and was due on October 10, 2023. Please find the invoice attached for you.r ref​erence.
@@ -2820,24 +3074,30 @@
 Attachment: the link</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>eph:12001#obf_high</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourism project management experience. This update includes:
@@ -2850,7 +3110,7 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Dear Marcus,
 We are glad to introduce our latest software update designed to enhance your eco-tourіsm proj3ct managem-ent experience. This update includes:
@@ -2863,24 +3123,30 @@
 Eco-Tour Software Innovations Team</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>eph:12580#obf_high</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hope this message finds you well. As we are in the critical stages of finalizing our current shipping routes optimization project, I need you to confirm your login credentials to grant you continued access to all necessary documents and platforms.
@@ -2892,7 +3158,7 @@
 Senior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Dear Megan,
 I hopе this message finds you well. As we are in the critical stages of finalizing our current 5hipping routеs optimization project, I nee.d you to confirm your login crede​ntials to grant you continued access to all necessary docu.ments and platfоrms.
@@ -2904,24 +3170,30 @@
 S3nior Executive, Gulf Coast Shipping Lines</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>eph:12678#obf_high</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Member,
 Our records indicate that your account is due for a mandatory security update. To prevent any disruption in service, we require you to reset your password immediately using the secure portal linked below:
@@ -2932,7 +3204,7 @@
 IT Department</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Dear Pacific Northwest Software Team Mеmber,
 Our records indicate that your account is due for a m4ndatory security upd4te. To рrevent any disruption in service, we requirе you to r3set your password immediately using the secure portal linkеd bel0w:
@@ -2943,24 +3215,30 @@
 IT Department</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>eph:12998#obf_high</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing well. I've sent over a crucial file pertaining to the CRM project that needs your input. It's essential to review this document as soon as possible to keep our timelines intact.
@@ -2970,7 +3248,7 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Hi Kelly,
 I hope you're doing wеll. I've se​nt ov​er a crucial file рertaining to the CRM pro​ject that needs your input. It's essential to review this documеnt as soon as possibl-e to keep our timelines intact.
@@ -2980,24 +3258,30 @@
 [Colleague's Name]</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>eph:13135#obf_high</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Hello James,
 We hope you're doing well. As a trusted provider, we are writing to inform you about a critical update for the marketing analysis tool your department frequently uses.
@@ -3008,7 +3292,7 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Hell.o James,
 We hope you're doing well. As a trusted pr-ovider, we are writing to inform you abоut a critical update for the marketing anal​ysis tоol your department frequently usеs.
@@ -3019,24 +3303,30 @@
 [Trusted Third-Party App Provider] Support Team</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>eph:13635#obf_high</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining robust security standards, it's critical that you review the attached document detailing the latest updates to our security protocols.
@@ -3047,7 +3337,7 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Hello Aaron,
 As part of our ongoing commitment to maintaining ro-bust security standаrds, it's critical th4t you review the attached doc-ument detailing the late​st upda.tes to our security protocols.
@@ -3058,24 +3348,30 @@
 IT Security Manager</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>eph:4299#obf_high</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>obf_high</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reaching out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sensitive nature, please arrange a transfer of €50,000 to the account provided in the link below by EOD.
@@ -3088,7 +3384,7 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Hi Mark,
 I’m reach.ing out with an urgent request regarding a critical payment to one of our major suppliers. Due to the time-sens​itive nature, please arrange a tran5fer of €50,000 to the account provided in the link below by EOD.
@@ -3101,18 +3397,16 @@
 Thuringia Equipment Supply Co.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="F2:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="readability" error="Enter one of 2, 1, 0 (see the Instructions sheet)" type="list">
-      <formula1>"2,1,0"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3125,63 +3419,54 @@
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12308#para_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -3192,7 +3477,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
@@ -3203,23 +3488,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:16367#para_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -3229,7 +3518,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
@@ -3239,23 +3528,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:11434#para_high</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hello David,
 I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
@@ -3266,7 +3559,7 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hello David,
 I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
@@ -3277,23 +3570,27 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12308#para_high</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -3304,7 +3601,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Hey James,
 Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
@@ -3315,23 +3612,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>partly</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:14108#para_high</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
@@ -3341,7 +3642,7 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
@@ -3351,23 +3652,27 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:15264#para_high</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hello Joel,
 Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
@@ -3378,7 +3683,7 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hello Joel,
 I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
@@ -3389,23 +3694,27 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:16367#para_high</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -3415,7 +3724,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
@@ -3425,23 +3734,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#para_high</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -3452,7 +3765,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
@@ -3463,14 +3776,13 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3483,63 +3795,54 @@
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12308#para_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -3550,7 +3853,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
@@ -3561,23 +3864,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:16367#para_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -3587,7 +3894,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
@@ -3597,23 +3904,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:11434#para_high</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hello David,
 I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
@@ -3624,7 +3935,7 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hello David,
 I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
@@ -3635,23 +3946,27 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12308#para_high</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -3662,7 +3977,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Hey James,
 Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
@@ -3673,23 +3988,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:14108#para_high</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
@@ -3699,7 +4018,7 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
@@ -3709,23 +4028,27 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:15264#para_high</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hello Joel,
 Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
@@ -3736,7 +4059,7 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hello Joel,
 I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
@@ -3747,23 +4070,27 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:16367#para_high</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -3773,7 +4100,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
@@ -3783,23 +4110,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#para_high</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -3810,7 +4141,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
@@ -3821,14 +4152,13 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3841,63 +4171,54 @@
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>row</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variant_id</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>condition</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>original_body</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>variant_body</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>eph:12308#para_low</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -3908,7 +4229,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. To ensure everything is set smoothly, could you please log into the internal server using the link below? A brief verification is required from your side.
@@ -3919,23 +4240,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>eph:16367#para_low</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>para_low</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -3945,7 +4270,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Should only take a moment. Here's the link: the link
@@ -3955,23 +4280,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>eph:11434#para_high</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Hello David,
 I hope this message finds you well. As we prepare for the next phase of our data analysis project, it is mandatory to confirm your login credentials to ensure seamless access to the analysis tools needed for your current project.
@@ -3982,7 +4311,7 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hello David,
 I trust this communication reaches you in good health. In anticipation of the forthcoming stage in our data analysis endeavor, it is imperative to verify your login details to guarantee uninterrupted utilization of the necessary analytical tools for your ongoing project.
@@ -3993,23 +4322,27 @@
 Senior Operations Analyst</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>eph:12308#para_high</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Hey James,
 Hope your day is going well! We're rolling out some updates to streamline our processes for the revamp project. To ensure everything is set smoothly, could you please log into the internal server using the link below? It just needs a quick check from your end.
@@ -4020,7 +4353,7 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Hey James,
 Wishing you a pleasant day ahead! We're implementing enhancements to optimize our workflows for the comprehensive overhaul initiative. For a seamless setup, kindly access the internal server by entering the credentials provided in the link. A brief verification is required from your side.
@@ -4031,23 +4364,27 @@
 (Senior Operations Manager)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>partly</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>eph:14108#para_high</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Great team meeting today! As discussed, I've compiled the key points and next steps. You can review the details by checking out the link below:
@@ -4057,7 +4394,7 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hi Callum,
 Outstanding team assembly today! In accordance with our previous discussion, I have organized the essential highlights and subsequent actions. You can examine the specifics by referring to the information provided in the link listed below:
@@ -4067,23 +4404,27 @@
 Alex Martins</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>eph:15264#para_high</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hello Joel,
 Hope you're well! I've attached the latest progress documents for the green manufacturing project we are working on. Please review at your convenience.
@@ -4094,7 +4435,7 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Hello Joel,
 I trust you're in good health! I have enclosed the most recent update files for the sustainable production initiative we are currently undertaking. Kindly peruse at your leisure.
@@ -4105,23 +4446,27 @@
 Sustainability Coordinator</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>eph:16367#para_high</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Hey Michael,
 Hope you're doing well! We're rolling out some new updates and I realized I need you to verify your credentials to grant access. Should only take a moment. Here's the link: the link
@@ -4131,7 +4476,7 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hey Michael,
 I trust you're in good spirits! We're about to launch fresh enhancements and it's come to my attention that you'll need to confirm your credentials to obtain entry. Will require a brief duration. Here's the link: the link
@@ -4141,23 +4486,27 @@
 Operations Team</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>eph:4123#para_high</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>para_high</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We've identified a critical issue with the network capabilities of your device that needs immediate attention. Our records indicate that your equipment might be experiencing malfunctions, which could interfere with your day-to-day operations.
@@ -4168,7 +4517,7 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dear Gerald,
 We have pinpointed a vital concern pertaining to the network functionalities of your equipment that necessitates prompt action. The data suggests that your machinery may be suffering from issues, potentially disrupting your routine business activities, as indicated by day.
@@ -4179,14 +4528,13 @@
 --- This message is intended for immediate action ---</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>preserved</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="meaning" error="Enter one of preserved, partly, not (see the Instructions sheet)" type="list">
-      <formula1>"preserved,partly,not"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>